--- a/CASE_Import_Template_Final.xlsx
+++ b/CASE_Import_Template_Final.xlsx
@@ -1,535 +1,536 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr filterPrivacy="1"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C5C54A-DEFF-4DA1-9988-FB1B534F14F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="General Information" state="visible" r:id="rId4"/>
-    <sheet sheetId="2" name="Victim Information" state="visible" r:id="rId5"/>
-    <sheet sheetId="3" name="Act and Sections" state="visible" r:id="rId6"/>
-    <sheet sheetId="4" name="Accused Detail" state="visible" r:id="rId7"/>
-    <sheet sheetId="5" name="Property Details" state="visible" r:id="rId8"/>
+    <sheet name="General Information" sheetId="1" r:id="rId1"/>
+    <sheet name="Victim Information" sheetId="2" r:id="rId2"/>
+    <sheet name="Act and Sections" sheetId="3" r:id="rId3"/>
+    <sheet name="Accused Detail" sheetId="4" r:id="rId4"/>
+    <sheet name="Property Details" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="340">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="341">
+  <si>
+    <t>linked_fir_dd_no</t>
+  </si>
+  <si>
+    <t>fir_date</t>
+  </si>
+  <si>
+    <t>disposal_type</t>
+  </si>
+  <si>
+    <t>district</t>
+  </si>
+  <si>
+    <t>police_station</t>
+  </si>
+  <si>
+    <t>local_head</t>
+  </si>
+  <si>
+    <t>case_type</t>
+  </si>
+  <si>
+    <t>beat_number</t>
+  </si>
+  <si>
+    <t>occurrence_date</t>
+  </si>
+  <si>
+    <t>occurrence_time</t>
+  </si>
+  <si>
+    <t>brief_facts</t>
+  </si>
+  <si>
+    <t>status_remarks</t>
+  </si>
+  <si>
+    <t>complainant_first_name</t>
+  </si>
+  <si>
+    <t>complainant_middle_name</t>
+  </si>
+  <si>
+    <t>complainant_last_name</t>
+  </si>
+  <si>
+    <t>complainant_nickname</t>
+  </si>
+  <si>
+    <t>complainant_gender</t>
+  </si>
+  <si>
+    <t>complainant_marital_status</t>
+  </si>
+  <si>
+    <t>complainant_relation_type</t>
+  </si>
+  <si>
+    <t>complainant_relative_name</t>
+  </si>
+  <si>
+    <t>complainant_mobile_country_code</t>
+  </si>
+  <si>
+    <t>complainant_mobile</t>
+  </si>
+  <si>
+    <t>complainant_qualification</t>
+  </si>
+  <si>
+    <t>complainant_dob</t>
+  </si>
+  <si>
+    <t>complainant_age_year</t>
+  </si>
+  <si>
+    <t>complainant_birth_year</t>
+  </si>
+  <si>
+    <t>complainant_house_no</t>
+  </si>
+  <si>
+    <t>complainant_street</t>
+  </si>
+  <si>
+    <t>complainant_colony</t>
+  </si>
+  <si>
+    <t>complainant_city_town_village</t>
+  </si>
+  <si>
+    <t>complainant_tehsil_block_mandal</t>
+  </si>
+  <si>
+    <t>complainant_present_address</t>
+  </si>
+  <si>
+    <t>complainant_country</t>
+  </si>
+  <si>
+    <t>complainant_state</t>
+  </si>
+  <si>
+    <t>complainant_district</t>
+  </si>
+  <si>
+    <t>complainant_police_station</t>
+  </si>
+  <si>
+    <t>complainant_pincode</t>
+  </si>
+  <si>
+    <t>complainant_perm_same</t>
+  </si>
+  <si>
+    <t>complainant_perm_house_no</t>
+  </si>
+  <si>
+    <t>complainant_perm_street</t>
+  </si>
+  <si>
+    <t>complainant_perm_colony</t>
+  </si>
+  <si>
+    <t>complainant_perm_city_town_village</t>
+  </si>
+  <si>
+    <t>complainant_perm_tehsil_block_mandal</t>
+  </si>
+  <si>
+    <t>complainant_perm_country</t>
+  </si>
+  <si>
+    <t>complainant_perm_state</t>
+  </si>
+  <si>
+    <t>complainant_perm_district</t>
+  </si>
+  <si>
+    <t>complainant_perm_police_station</t>
+  </si>
+  <si>
+    <t>complainant_perm_pincode</t>
+  </si>
+  <si>
+    <t>occurrence_house_no</t>
+  </si>
+  <si>
+    <t>occurrence_street</t>
+  </si>
+  <si>
+    <t>occurrence_colony</t>
+  </si>
+  <si>
+    <t>occurrence_city_town_village</t>
+  </si>
+  <si>
+    <t>occurrence_tehsil_block_mandal</t>
+  </si>
+  <si>
+    <t>occurrence_country</t>
+  </si>
+  <si>
+    <t>occurrence_state</t>
+  </si>
+  <si>
+    <t>occurrence_district</t>
+  </si>
+  <si>
+    <t>occurrence_police_station</t>
+  </si>
+  <si>
+    <t>occurrence_pincode</t>
+  </si>
+  <si>
+    <t>io_name</t>
+  </si>
+  <si>
+    <t>io_pis</t>
+  </si>
+  <si>
+    <t>io_rank</t>
+  </si>
+  <si>
+    <t>io_mobile</t>
+  </si>
+  <si>
+    <t>General Information</t>
+  </si>
+  <si>
+    <t>Complainant Personal Details</t>
+  </si>
+  <si>
+    <t>Complainant Present Address</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Address</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Address</t>
+  </si>
+  <si>
+    <t>IO Details</t>
+  </si>
+  <si>
+    <t>FIR Number</t>
+  </si>
+  <si>
+    <t>FIR Date and time</t>
+  </si>
+  <si>
+    <t>Disposal Type</t>
+  </si>
+  <si>
+    <t>District</t>
+  </si>
+  <si>
+    <t>Police Station</t>
+  </si>
+  <si>
+    <t>Local Head (Crime)</t>
+  </si>
+  <si>
+    <t>Case Registration Type</t>
+  </si>
+  <si>
+    <t>Beat Number</t>
+  </si>
+  <si>
+    <t>Date of Occurrence</t>
+  </si>
+  <si>
+    <t>Occurrence Time</t>
+  </si>
+  <si>
+    <t>Brief Facts of the Case</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status </t>
+  </si>
+  <si>
+    <t>Complainant First Name</t>
+  </si>
+  <si>
+    <t>Complainant Middle Name</t>
+  </si>
+  <si>
+    <t>Complainant Last Name</t>
+  </si>
+  <si>
+    <t>Complainant Nickname(s)</t>
+  </si>
+  <si>
+    <t>Complainant Gender</t>
+  </si>
+  <si>
+    <t>Complainant Marital Status</t>
+  </si>
+  <si>
+    <t>Complainant Relation Type</t>
+  </si>
+  <si>
+    <t>Complainant Relative Name</t>
+  </si>
+  <si>
+    <t>Complainant Mobile Country Code</t>
+  </si>
+  <si>
+    <t>Complainant Mobile No.</t>
+  </si>
+  <si>
+    <t>Complainant Qualification</t>
+  </si>
+  <si>
+    <t>Complainant Date of Birth</t>
+  </si>
+  <si>
+    <t>Complainant Age (Years)</t>
+  </si>
+  <si>
+    <t>Complainant Year of Birth</t>
+  </si>
+  <si>
+    <t>Complainant House No.</t>
+  </si>
+  <si>
+    <t>Complainant Street</t>
+  </si>
+  <si>
+    <t>Complainant Colony</t>
+  </si>
+  <si>
+    <t>Complainant Village / City / Town</t>
+  </si>
+  <si>
+    <t>Complainant Tehsil / Block / Mandal</t>
+  </si>
+  <si>
+    <t>Complainant Full Present Address</t>
+  </si>
+  <si>
+    <t>Complainant Nationality</t>
+  </si>
+  <si>
+    <t>Complainant State</t>
+  </si>
+  <si>
+    <t>Complainant District</t>
+  </si>
+  <si>
+    <t>Complainant Police Station</t>
+  </si>
+  <si>
+    <t>Complainant Pin Code</t>
+  </si>
+  <si>
+    <t>Is Permanent Address same as Present Address?</t>
+  </si>
+  <si>
+    <t>Complainant Permanent House No.</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Street</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Colony</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Village / City / Town</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Tehsil / Block / Mandal</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Nationality</t>
+  </si>
+  <si>
+    <t>Complainant Permanent State</t>
+  </si>
+  <si>
+    <t>Complainant Permanent District</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Police Station</t>
+  </si>
+  <si>
+    <t>Complainant Permanent Pin Code</t>
+  </si>
+  <si>
+    <t>Place of Occurrence House No.</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Street</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Colony</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Village / City / Town</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Tehsil / Block / Mandal</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Address Nationality</t>
+  </si>
+  <si>
+    <t>Place of Occurrence State</t>
+  </si>
+  <si>
+    <t>Place of Occurrence District</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Police Station</t>
+  </si>
+  <si>
+    <t>Place of Occurrence Pin Code</t>
+  </si>
+  <si>
+    <t>IO / Officer Name</t>
+  </si>
+  <si>
+    <t>PIS No. of IO</t>
+  </si>
+  <si>
+    <t>IO Rank</t>
+  </si>
+  <si>
+    <t>IO Mobile No.</t>
+  </si>
+  <si>
+    <t>e.g. FIR-220/2026</t>
+  </si>
+  <si>
+    <t>YYYY-MM-DD</t>
+  </si>
+  <si>
+    <t>e.g. New Delhi District (NDD)</t>
+  </si>
+  <si>
+    <t>e.g. Parliament Street</t>
+  </si>
+  <si>
+    <t>e.g. Theft / Larceny</t>
+  </si>
+  <si>
+    <t>e.g. Section 379 IPC</t>
+  </si>
+  <si>
+    <t>e.g. Property Theft</t>
+  </si>
+  <si>
+    <t>e.g. SID-889021</t>
+  </si>
+  <si>
+    <t>e.g. CCTNS-202699104</t>
+  </si>
+  <si>
+    <t>e.g. Beat No. 4</t>
+  </si>
+  <si>
+    <t>e.g. Patel Chowk Metro parking</t>
+  </si>
+  <si>
+    <t>Incident narrative</t>
+  </si>
+  <si>
+    <t>e.g. Under investigation</t>
+  </si>
+  <si>
+    <t>NPR Number</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Middle Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Nickname or alias</t>
+  </si>
+  <si>
+    <t>select: Male, Female, Transgender, Unknown</t>
+  </si>
+  <si>
+    <t>select: Married, Unmarried, Divorced, Widowed, Single, Unknown</t>
+  </si>
+  <si>
+    <t>select: Father, Mother, Husband, Wife, Guardian, Other</t>
+  </si>
+  <si>
+    <t>Father's or Husband's Name</t>
+  </si>
+  <si>
+    <t>e.g. +91</t>
+  </si>
+  <si>
+    <t>10-digit mobile number</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Min age</t>
+  </si>
+  <si>
+    <t>Max age</t>
+  </si>
+  <si>
+    <t>House Number</t>
+  </si>
+  <si>
+    <t>Street name</t>
+  </si>
+  <si>
+    <t>Colony name</t>
+  </si>
+  <si>
+    <t>Village/City</t>
+  </si>
+  <si>
+    <t>Tehsil</t>
+  </si>
+  <si>
+    <t>Full residential address</t>
+  </si>
+  <si>
+    <t>select: Indian, Nepalese, Bhutanese, Bangladeshi, Pakistani, Sri Lankan, Afghan, Myanmar, Tibetan, American, British, Canadian, Other</t>
+  </si>
+  <si>
+    <t>select: Andhra Pradesh, Arunachal Pradesh, Assam, Bihar, Chhattisgarh, Delhi, Goa, Gujarat, Haryana, Himachal Pradesh, Jammu &amp; Kashmir, Jharkhand, Karnataka, Kerala, Ladakh, Madhya Pradesh, Maharashtra, Manipur, Meghalaya, Mizoram, Nagaland, Odisha, Puducherry, Punjab, Rajasthan, Sikkim, Tamil Nadu, Telangana, Tripura, Uttar Pradesh, Uttarakhand, West Bengal, Other UT/State</t>
+  </si>
+  <si>
+    <t>select: South District (SD), South East District (SED), New Delhi District (NDD), South West District (SWD), West District (WD), Outer District (OD), Dwarka District (DW), North West District (NWD), Rohini District (RND), Outer North District (OND), Central District (CD), North District (ND), East District (ED), North East District (NED), Shahdara District (SHD)</t>
+  </si>
+  <si>
+    <t>6-digit PIN code</t>
+  </si>
+  <si>
+    <t>boolean</t>
+  </si>
+  <si>
+    <t>e.g. Inspector Ravindra Singh</t>
+  </si>
   <si>
     <t>fir_no</t>
   </si>
   <si>
-    <t>fir_date</t>
-  </si>
-  <si>
-    <t>disposal_type</t>
-  </si>
-  <si>
-    <t>district</t>
-  </si>
-  <si>
-    <t>police_station</t>
-  </si>
-  <si>
-    <t>local_head</t>
-  </si>
-  <si>
-    <t>case_type</t>
-  </si>
-  <si>
-    <t>beat_number</t>
-  </si>
-  <si>
-    <t>occurrence_date</t>
-  </si>
-  <si>
-    <t>occurrence_time</t>
-  </si>
-  <si>
-    <t>brief_facts</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>complainant_first_name</t>
-  </si>
-  <si>
-    <t>complainant_middle_name</t>
-  </si>
-  <si>
-    <t>complainant_last_name</t>
-  </si>
-  <si>
-    <t>complainant_nickname</t>
-  </si>
-  <si>
-    <t>complainant_gender</t>
-  </si>
-  <si>
-    <t>complainant_marital_status</t>
-  </si>
-  <si>
-    <t>complainant_relation_type</t>
-  </si>
-  <si>
-    <t>complainant_relative_name</t>
-  </si>
-  <si>
-    <t>complainant_mobile_country_code</t>
-  </si>
-  <si>
-    <t>complainant_mobile</t>
-  </si>
-  <si>
-    <t>complainant_qualification</t>
-  </si>
-  <si>
-    <t>complainant_dob</t>
-  </si>
-  <si>
-    <t>complainant_age_year</t>
-  </si>
-  <si>
-    <t>complainant_birth_year</t>
-  </si>
-  <si>
-    <t>complainant_house_no</t>
-  </si>
-  <si>
-    <t>complainant_street</t>
-  </si>
-  <si>
-    <t>complainant_colony</t>
-  </si>
-  <si>
-    <t>complainant_city_town_village</t>
-  </si>
-  <si>
-    <t>complainant_tehsil_block_mandal</t>
-  </si>
-  <si>
-    <t>complainant_present_address</t>
-  </si>
-  <si>
-    <t>complainant_country</t>
-  </si>
-  <si>
-    <t>complainant_state</t>
-  </si>
-  <si>
-    <t>complainant_district</t>
-  </si>
-  <si>
-    <t>complainant_police_station</t>
-  </si>
-  <si>
-    <t>complainant_pincode</t>
-  </si>
-  <si>
-    <t>complainant_perm_same</t>
-  </si>
-  <si>
-    <t>complainant_perm_house_no</t>
-  </si>
-  <si>
-    <t>complainant_perm_street</t>
-  </si>
-  <si>
-    <t>complainant_perm_colony</t>
-  </si>
-  <si>
-    <t>complainant_perm_city_town_village</t>
-  </si>
-  <si>
-    <t>complainant_perm_tehsil_block_mandal</t>
-  </si>
-  <si>
-    <t>complainant_perm_country</t>
-  </si>
-  <si>
-    <t>complainant_perm_state</t>
-  </si>
-  <si>
-    <t>complainant_perm_district</t>
-  </si>
-  <si>
-    <t>complainant_perm_police_station</t>
-  </si>
-  <si>
-    <t>complainant_perm_pincode</t>
-  </si>
-  <si>
-    <t>occurrence_house_no</t>
-  </si>
-  <si>
-    <t>occurrence_street</t>
-  </si>
-  <si>
-    <t>occurrence_colony</t>
-  </si>
-  <si>
-    <t>occurrence_city_town_village</t>
-  </si>
-  <si>
-    <t>occurrence_tehsil_block_mandal</t>
-  </si>
-  <si>
-    <t>occurrence_country</t>
-  </si>
-  <si>
-    <t>occurrence_state</t>
-  </si>
-  <si>
-    <t>occurrence_district</t>
-  </si>
-  <si>
-    <t>occurrence_police_station</t>
-  </si>
-  <si>
-    <t>occurrence_pincode</t>
-  </si>
-  <si>
-    <t>io_name</t>
-  </si>
-  <si>
-    <t>io_pis</t>
-  </si>
-  <si>
-    <t>io_rank</t>
-  </si>
-  <si>
-    <t>io_mobile</t>
-  </si>
-  <si>
-    <t>General Information</t>
-  </si>
-  <si>
-    <t>Complainant Personal Details</t>
-  </si>
-  <si>
-    <t>Complainant Present Address</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Address</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Address</t>
-  </si>
-  <si>
-    <t>IO Details</t>
-  </si>
-  <si>
-    <t>FIR Number</t>
-  </si>
-  <si>
-    <t>FIR Date and time</t>
-  </si>
-  <si>
-    <t>Disposal Type</t>
-  </si>
-  <si>
-    <t>District</t>
-  </si>
-  <si>
-    <t>Police Station</t>
-  </si>
-  <si>
-    <t>Local Head (Crime)</t>
-  </si>
-  <si>
-    <t>Case Registration Type</t>
-  </si>
-  <si>
-    <t>Beat Number</t>
-  </si>
-  <si>
-    <t>Date of Occurrence</t>
-  </si>
-  <si>
-    <t>Occurrence Time</t>
-  </si>
-  <si>
-    <t>Brief Facts of the Case</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status </t>
-  </si>
-  <si>
-    <t>Complainant First Name</t>
-  </si>
-  <si>
-    <t>Complainant Middle Name</t>
-  </si>
-  <si>
-    <t>Complainant Last Name</t>
-  </si>
-  <si>
-    <t>Complainant Nickname(s)</t>
-  </si>
-  <si>
-    <t>Complainant Gender</t>
-  </si>
-  <si>
-    <t>Complainant Marital Status</t>
-  </si>
-  <si>
-    <t>Complainant Relation Type</t>
-  </si>
-  <si>
-    <t>Complainant Relative Name</t>
-  </si>
-  <si>
-    <t>Complainant Mobile Country Code</t>
-  </si>
-  <si>
-    <t>Complainant Mobile No.</t>
-  </si>
-  <si>
-    <t>Complainant Qualification</t>
-  </si>
-  <si>
-    <t>Complainant Date of Birth</t>
-  </si>
-  <si>
-    <t>Complainant Age (Years)</t>
-  </si>
-  <si>
-    <t>Complainant Year of Birth</t>
-  </si>
-  <si>
-    <t>Complainant House No.</t>
-  </si>
-  <si>
-    <t>Complainant Street</t>
-  </si>
-  <si>
-    <t>Complainant Colony</t>
-  </si>
-  <si>
-    <t>Complainant Village / City / Town</t>
-  </si>
-  <si>
-    <t>Complainant Tehsil / Block / Mandal</t>
-  </si>
-  <si>
-    <t>Complainant Full Present Address</t>
-  </si>
-  <si>
-    <t>Complainant Nationality</t>
-  </si>
-  <si>
-    <t>Complainant State</t>
-  </si>
-  <si>
-    <t>Complainant District</t>
-  </si>
-  <si>
-    <t>Complainant Police Station</t>
-  </si>
-  <si>
-    <t>Complainant Pin Code</t>
-  </si>
-  <si>
-    <t>Is Permanent Address same as Present Address?</t>
-  </si>
-  <si>
-    <t>Complainant Permanent House No.</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Street</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Colony</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Village / City / Town</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Tehsil / Block / Mandal</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Nationality</t>
-  </si>
-  <si>
-    <t>Complainant Permanent State</t>
-  </si>
-  <si>
-    <t>Complainant Permanent District</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Police Station</t>
-  </si>
-  <si>
-    <t>Complainant Permanent Pin Code</t>
-  </si>
-  <si>
-    <t>Place of Occurrence House No.</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Street</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Colony</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Village / City / Town</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Tehsil / Block / Mandal</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Address Nationality</t>
-  </si>
-  <si>
-    <t>Place of Occurrence State</t>
-  </si>
-  <si>
-    <t>Place of Occurrence District</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Police Station</t>
-  </si>
-  <si>
-    <t>Place of Occurrence Pin Code</t>
-  </si>
-  <si>
-    <t>IO / Officer Name</t>
-  </si>
-  <si>
-    <t>PIS No. of IO</t>
-  </si>
-  <si>
-    <t>IO Rank</t>
-  </si>
-  <si>
-    <t>IO Mobile No.</t>
-  </si>
-  <si>
-    <t>e.g. FIR-220/2026</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-  <si>
-    <t>e.g. New Delhi District (NDD)</t>
-  </si>
-  <si>
-    <t>e.g. Parliament Street</t>
-  </si>
-  <si>
-    <t>e.g. Theft / Larceny</t>
-  </si>
-  <si>
-    <t>e.g. Section 379 IPC</t>
-  </si>
-  <si>
-    <t>e.g. Property Theft</t>
-  </si>
-  <si>
-    <t>e.g. SID-889021</t>
-  </si>
-  <si>
-    <t>e.g. CCTNS-202699104</t>
-  </si>
-  <si>
-    <t>e.g. Beat No. 4</t>
-  </si>
-  <si>
-    <t>e.g. Patel Chowk Metro parking</t>
-  </si>
-  <si>
-    <t>Incident narrative</t>
-  </si>
-  <si>
-    <t>e.g. Under investigation</t>
-  </si>
-  <si>
-    <t>NPR Number</t>
-  </si>
-  <si>
-    <t>First Name</t>
-  </si>
-  <si>
-    <t>Middle Name</t>
-  </si>
-  <si>
-    <t>Last Name</t>
-  </si>
-  <si>
-    <t>Nickname or alias</t>
-  </si>
-  <si>
-    <t>select: Male, Female, Transgender, Unknown</t>
-  </si>
-  <si>
-    <t>select: Married, Unmarried, Divorced, Widowed, Single, Unknown</t>
-  </si>
-  <si>
-    <t>select: Father, Mother, Husband, Wife, Guardian, Other</t>
-  </si>
-  <si>
-    <t>Father's or Husband's Name</t>
-  </si>
-  <si>
-    <t>e.g. +91</t>
-  </si>
-  <si>
-    <t>10-digit mobile number</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Min age</t>
-  </si>
-  <si>
-    <t>Max age</t>
-  </si>
-  <si>
-    <t>House Number</t>
-  </si>
-  <si>
-    <t>Street name</t>
-  </si>
-  <si>
-    <t>Colony name</t>
-  </si>
-  <si>
-    <t>Village/City</t>
-  </si>
-  <si>
-    <t>Tehsil</t>
-  </si>
-  <si>
-    <t>Full residential address</t>
-  </si>
-  <si>
-    <t>select: Indian, Nepalese, Bhutanese, Bangladeshi, Pakistani, Sri Lankan, Afghan, Myanmar, Tibetan, American, British, Canadian, Other</t>
-  </si>
-  <si>
-    <t>select: Andhra Pradesh, Arunachal Pradesh, Assam, Bihar, Chhattisgarh, Delhi, Goa, Gujarat, Haryana, Himachal Pradesh, Jammu &amp; Kashmir, Jharkhand, Karnataka, Kerala, Ladakh, Madhya Pradesh, Maharashtra, Manipur, Meghalaya, Mizoram, Nagaland, Odisha, Puducherry, Punjab, Rajasthan, Sikkim, Tamil Nadu, Telangana, Tripura, Uttar Pradesh, Uttarakhand, West Bengal, Other UT/State</t>
-  </si>
-  <si>
-    <t>select: South District (SD), South East District (SED), New Delhi District (NDD), South West District (SWD), West District (WD), Outer District (OD), Dwarka District (DW), North West District (NWD), Rohini District (RND), Outer North District (OND), Central District (CD), North District (ND), East District (ED), North East District (NED), Shahdara District (SHD)</t>
-  </si>
-  <si>
-    <t>6-digit PIN code</t>
-  </si>
-  <si>
-    <t>boolean</t>
-  </si>
-  <si>
-    <t>e.g. Inspector Ravindra Singh</t>
-  </si>
-  <si>
-    <t>victim_npr</t>
-  </si>
-  <si>
     <t>victim_first_name</t>
   </si>
   <si>
@@ -602,6 +603,9 @@
     <t>victim_pincode</t>
   </si>
   <si>
+    <t>victim_perm_same</t>
+  </si>
+  <si>
     <t>victim_perm_house_no</t>
   </si>
   <si>
@@ -635,18 +639,12 @@
     <t>Case Reference</t>
   </si>
   <si>
-    <t>Victim Personal Details</t>
-  </si>
-  <si>
     <t>Victim Present Address</t>
   </si>
   <si>
     <t>Victim Permanent Address</t>
   </si>
   <si>
-    <t>Victim NPR No.</t>
-  </si>
-  <si>
     <t>Victim First Name</t>
   </si>
   <si>
@@ -866,6 +864,9 @@
     <t>accused_pincode</t>
   </si>
   <si>
+    <t>accused_perm_same</t>
+  </si>
+  <si>
     <t>accused_perm_house_no</t>
   </si>
   <si>
@@ -1014,6 +1015,9 @@
   </si>
   <si>
     <t>property_stolen_recovered</t>
+  </si>
+  <si>
+    <t>property_value</t>
   </si>
   <si>
     <t>Property Details</t>
@@ -1043,25 +1047,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <sz val="11"/>
       <color rgb="FF6B7280"/>
-      <sz val="11"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1095,7 +1099,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1106,6 +1110,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1446,9 +1453,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BP4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:BJ4"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="23" customWidth="1"/>
@@ -1487,7 +1494,7 @@
     <col min="62" max="62" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.4" customHeight="1" hidden="1" spans="1:68" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:62" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1675,83 +1682,83 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+    <row r="2" spans="1:62" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2" t="s">
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
+      <c r="AA2" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
-      <c r="AL2" s="2"/>
-      <c r="AM2" s="2" t="s">
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
+      <c r="AK2" s="6"/>
+      <c r="AL2" s="6"/>
+      <c r="AM2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="AN2" s="2"/>
-      <c r="AO2" s="2"/>
-      <c r="AP2" s="2"/>
-      <c r="AQ2" s="2"/>
-      <c r="AR2" s="2"/>
-      <c r="AS2" s="2"/>
-      <c r="AT2" s="2"/>
-      <c r="AU2" s="2"/>
-      <c r="AV2" s="2"/>
-      <c r="AW2" s="2" t="s">
+      <c r="AN2" s="6"/>
+      <c r="AO2" s="6"/>
+      <c r="AP2" s="6"/>
+      <c r="AQ2" s="6"/>
+      <c r="AR2" s="6"/>
+      <c r="AS2" s="6"/>
+      <c r="AT2" s="6"/>
+      <c r="AU2" s="6"/>
+      <c r="AV2" s="6"/>
+      <c r="AW2" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="AX2" s="2"/>
-      <c r="AY2" s="2"/>
-      <c r="AZ2" s="2"/>
-      <c r="BA2" s="2"/>
-      <c r="BB2" s="2"/>
-      <c r="BC2" s="2"/>
-      <c r="BD2" s="2"/>
-      <c r="BE2" s="2"/>
-      <c r="BF2" s="2"/>
-      <c r="BG2" s="2" t="s">
+      <c r="AX2" s="6"/>
+      <c r="AY2" s="6"/>
+      <c r="AZ2" s="6"/>
+      <c r="BA2" s="6"/>
+      <c r="BB2" s="6"/>
+      <c r="BC2" s="6"/>
+      <c r="BD2" s="6"/>
+      <c r="BE2" s="6"/>
+      <c r="BF2" s="6"/>
+      <c r="BG2" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="BH2" s="2"/>
-      <c r="BI2" s="2"/>
-      <c r="BJ2" s="2"/>
+      <c r="BH2" s="6"/>
+      <c r="BI2" s="6"/>
+      <c r="BJ2" s="6"/>
     </row>
-    <row r="3" ht="19.95" customHeight="1" spans="1:68" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:62" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
@@ -1939,7 +1946,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" ht="16.05" customHeight="1" spans="1:66" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:62" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>130</v>
       </c>
@@ -2125,205 +2132,199 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="BG2:BJ2"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="M2:Z2"/>
     <mergeCell ref="AA2:AL2"/>
     <mergeCell ref="AM2:AV2"/>
     <mergeCell ref="AW2:BF2"/>
-    <mergeCell ref="BG2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AK4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:AJ4"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
-    <col min="2" max="6" width="27" customWidth="1"/>
-    <col min="7" max="9" width="45" customWidth="1"/>
-    <col min="10" max="10" width="30" customWidth="1"/>
-    <col min="11" max="15" width="27" customWidth="1"/>
-    <col min="16" max="18" width="26" customWidth="1"/>
-    <col min="19" max="19" width="32" customWidth="1"/>
-    <col min="20" max="20" width="34" customWidth="1"/>
-    <col min="21" max="21" width="31" customWidth="1"/>
-    <col min="22" max="24" width="45" customWidth="1"/>
-    <col min="25" max="26" width="26" customWidth="1"/>
-    <col min="27" max="27" width="45" customWidth="1"/>
-    <col min="28" max="28" width="30" customWidth="1"/>
-    <col min="29" max="30" width="28" customWidth="1"/>
-    <col min="31" max="31" width="42" customWidth="1"/>
-    <col min="32" max="32" width="44" customWidth="1"/>
-    <col min="33" max="35" width="45" customWidth="1"/>
-    <col min="36" max="36" width="35" customWidth="1"/>
-    <col min="37" max="37" width="29" customWidth="1"/>
+    <col min="2" max="5" width="27" customWidth="1"/>
+    <col min="6" max="8" width="45" customWidth="1"/>
+    <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="14" width="27" customWidth="1"/>
+    <col min="15" max="17" width="26" customWidth="1"/>
+    <col min="18" max="18" width="32" customWidth="1"/>
+    <col min="19" max="19" width="34" customWidth="1"/>
+    <col min="20" max="20" width="31" customWidth="1"/>
+    <col min="21" max="23" width="45" customWidth="1"/>
+    <col min="24" max="25" width="26" customWidth="1"/>
+    <col min="26" max="26" width="45" customWidth="1"/>
+    <col min="27" max="27" width="30" customWidth="1"/>
+    <col min="28" max="29" width="28" customWidth="1"/>
+    <col min="30" max="30" width="42" customWidth="1"/>
+    <col min="31" max="31" width="44" customWidth="1"/>
+    <col min="32" max="34" width="45" customWidth="1"/>
+    <col min="35" max="35" width="35" customWidth="1"/>
+    <col min="36" max="36" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="B1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="I1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="J1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="K1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="L1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="M1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="P1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="Q1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="R1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="S1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="T1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="U1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="V1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="W1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="X1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="Y1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="Z1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AA1" t="s">
-        <v>37</v>
+        <v>195</v>
       </c>
       <c r="AB1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AC1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AD1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AE1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AF1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AH1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AI1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AJ1" t="s">
-        <v>202</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2" t="s">
+      <c r="B2" s="6"/>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
-      <c r="AA2" s="2" t="s">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
-      <c r="AK2" s="2"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
     </row>
-    <row r="3" ht="19.95" customHeight="1" spans="1:37" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
@@ -2400,10 +2401,10 @@
         <v>231</v>
       </c>
       <c r="Z3" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA3" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="AB3" s="3" t="s">
         <v>233</v>
@@ -2432,138 +2433,132 @@
       <c r="AJ3" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="AK3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:36" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="4" ht="16.05" customHeight="1" spans="1:37" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+      <c r="B4" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="M4" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>151</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="N4" s="5" t="s">
         <v>244</v>
       </c>
       <c r="O4" s="5" t="s">
-        <v>245</v>
+        <v>157</v>
       </c>
       <c r="P4" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="U4" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="AA4" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="Q4" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="R4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="S4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="T4" s="5" t="s">
+      <c r="AE4" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="U4" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="V4" s="5" t="s">
+      <c r="AF4" s="5" t="s">
         <v>163</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="AG4" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="AH4" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="AI4" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="AE4" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="AF4" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="AG4" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="AH4" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="AI4" s="5" t="s">
-        <v>165</v>
-      </c>
       <c r="AJ4" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="AK4" s="5" t="s">
         <v>166</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B2:O2"/>
-    <mergeCell ref="P2:Z2"/>
-    <mergeCell ref="AA2:AK2"/>
+    <mergeCell ref="B2:N2"/>
+    <mergeCell ref="O2:Y2"/>
+    <mergeCell ref="Z2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="3" width="20" customWidth="1"/>
@@ -2571,62 +2566,62 @@
     <col min="5" max="5" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="B1" t="s">
+        <v>245</v>
+      </c>
+      <c r="C1" t="s">
         <v>246</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>247</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>248</v>
       </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="E2" s="6"/>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E2" s="2"/>
-    </row>
-    <row r="3" ht="19.95" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:5" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>254</v>
       </c>
-    </row>
-    <row r="4" ht="16.05" customHeight="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>256</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>257</v>
       </c>
     </row>
   </sheetData>
@@ -2635,14 +2630,14 @@
     <mergeCell ref="D2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:AJ4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="5" width="28" customWidth="1"/>
@@ -2664,84 +2659,84 @@
     <col min="36" max="36" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="B1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" t="s">
         <v>258</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>259</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>260</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>261</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>262</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>263</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>264</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>265</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>266</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>267</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>268</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>269</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>270</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>271</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>272</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>273</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>274</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>275</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>276</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>277</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>278</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>279</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>280</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>281</v>
-      </c>
-      <c r="Z1" t="s">
-        <v>37</v>
       </c>
       <c r="AA1" t="s">
         <v>282</v>
@@ -2774,53 +2769,53 @@
         <v>291</v>
       </c>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2" t="s">
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6" t="s">
         <v>293</v>
       </c>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2" t="s">
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="AA2" s="2"/>
-      <c r="AB2" s="2"/>
-      <c r="AC2" s="2"/>
-      <c r="AD2" s="2"/>
-      <c r="AE2" s="2"/>
-      <c r="AF2" s="2"/>
-      <c r="AG2" s="2"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="2"/>
-      <c r="AJ2" s="2"/>
+      <c r="AA2" s="6"/>
+      <c r="AB2" s="6"/>
+      <c r="AC2" s="6"/>
+      <c r="AD2" s="6"/>
+      <c r="AE2" s="6"/>
+      <c r="AF2" s="6"/>
+      <c r="AG2" s="6"/>
+      <c r="AH2" s="6"/>
+      <c r="AI2" s="6"/>
+      <c r="AJ2" s="6"/>
     </row>
-    <row r="3" ht="19.95" customHeight="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
@@ -2930,9 +2925,9 @@
         <v>328</v>
       </c>
     </row>
-    <row r="4" ht="16.05" customHeight="1" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>144</v>
@@ -2968,10 +2963,10 @@
         <v>131</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>243</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>245</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>157</v>
@@ -3047,14 +3042,14 @@
     <mergeCell ref="Z2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
@@ -3062,9 +3057,9 @@
     <col min="5" max="5" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>169</v>
       </c>
       <c r="B1" t="s">
         <v>329</v>
@@ -3075,68 +3070,65 @@
       <c r="D1" t="s">
         <v>331</v>
       </c>
+      <c r="E1" t="s">
+        <v>332</v>
+      </c>
     </row>
-    <row r="2" ht="25" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2" s="6"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="6"/>
     </row>
-    <row r="3" ht="19.95" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
-    <row r="4" ht="16.05" customHeight="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" sqref="B10:B1000">
+  <dataValidations count="2">
+    <dataValidation type="list" allowBlank="1" sqref="B5:B1000" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"Vehicle,Mobile Phone,Cash,Jewellery,Electronics,Documents,Drugs,Arms,Others"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B5:B1000">
-      <formula1>"Vehicle,Mobile Phone,Cash,Jewellery,Electronics,Documents,Drugs,Arms,Others"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D10:D1000">
-      <formula1>"Stolen,Recovered,Involved,Seized"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D5:D1000">
+    <dataValidation type="list" allowBlank="1" sqref="D5:D1000" xr:uid="{00000000-0002-0000-0400-000002000000}">
       <formula1>"Stolen,Recovered,Involved,Seized"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
 </file>
--- a/CASE_Import_Template_Final.xlsx
+++ b/CASE_Import_Template_Final.xlsx
@@ -1,27 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95C5C54A-DEFF-4DA1-9988-FB1B534F14F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="General Information" sheetId="1" r:id="rId1"/>
-    <sheet name="Victim Information" sheetId="2" r:id="rId2"/>
-    <sheet name="Act and Sections" sheetId="3" r:id="rId3"/>
-    <sheet name="Accused Detail" sheetId="4" r:id="rId4"/>
-    <sheet name="Property Details" sheetId="5" r:id="rId5"/>
+    <sheet sheetId="1" name="General Information" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Victim Information" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Act and Sections" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Accused Detail" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Property Details" state="visible" r:id="rId8"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="341">
-  <si>
-    <t>linked_fir_dd_no</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="340">
+  <si>
+    <t>fir_no</t>
   </si>
   <si>
     <t>fir_date</t>
@@ -526,9 +525,6 @@
   </si>
   <si>
     <t>e.g. Inspector Ravindra Singh</t>
-  </si>
-  <si>
-    <t>fir_no</t>
   </si>
   <si>
     <t>victim_first_name</t>
@@ -1047,25 +1043,25 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <color rgb="FF6B7280"/>
       <sz val="11"/>
-      <color rgb="FF6B7280"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -1099,7 +1095,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1110,9 +1106,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1453,9 +1446,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BJ4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="3" width="23" customWidth="1"/>
@@ -1494,7 +1487,7 @@
     <col min="62" max="62" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:62" ht="14.4" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="14.4" customHeight="1" hidden="1" spans="1:62" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1682,83 +1675,83 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:62" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+    <row r="2" ht="25.05" customHeight="1" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6" t="s">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6"/>
-      <c r="AA2" s="6" t="s">
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-      <c r="AK2" s="6"/>
-      <c r="AL2" s="6"/>
-      <c r="AM2" s="6" t="s">
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="AN2" s="6"/>
-      <c r="AO2" s="6"/>
-      <c r="AP2" s="6"/>
-      <c r="AQ2" s="6"/>
-      <c r="AR2" s="6"/>
-      <c r="AS2" s="6"/>
-      <c r="AT2" s="6"/>
-      <c r="AU2" s="6"/>
-      <c r="AV2" s="6"/>
-      <c r="AW2" s="6" t="s">
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
+      <c r="AT2" s="2"/>
+      <c r="AU2" s="2"/>
+      <c r="AV2" s="2"/>
+      <c r="AW2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="AX2" s="6"/>
-      <c r="AY2" s="6"/>
-      <c r="AZ2" s="6"/>
-      <c r="BA2" s="6"/>
-      <c r="BB2" s="6"/>
-      <c r="BC2" s="6"/>
-      <c r="BD2" s="6"/>
-      <c r="BE2" s="6"/>
-      <c r="BF2" s="6"/>
-      <c r="BG2" s="6" t="s">
+      <c r="AX2" s="2"/>
+      <c r="AY2" s="2"/>
+      <c r="AZ2" s="2"/>
+      <c r="BA2" s="2"/>
+      <c r="BB2" s="2"/>
+      <c r="BC2" s="2"/>
+      <c r="BD2" s="2"/>
+      <c r="BE2" s="2"/>
+      <c r="BF2" s="2"/>
+      <c r="BG2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="BH2" s="6"/>
-      <c r="BI2" s="6"/>
-      <c r="BJ2" s="6"/>
+      <c r="BH2" s="2"/>
+      <c r="BI2" s="2"/>
+      <c r="BJ2" s="2"/>
     </row>
-    <row r="3" spans="1:62" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="19.95" customHeight="1" spans="1:62" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
@@ -1946,7 +1939,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="4" spans="1:62" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="16.05" customHeight="1" spans="1:62" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>130</v>
       </c>
@@ -2132,22 +2125,22 @@
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="BG2:BJ2"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="M2:Z2"/>
     <mergeCell ref="AA2:AL2"/>
     <mergeCell ref="AM2:AV2"/>
     <mergeCell ref="AW2:BF2"/>
+    <mergeCell ref="BG2:BJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="5" width="27" customWidth="1"/>
@@ -2170,273 +2163,273 @@
     <col min="36" max="36" width="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="1" hidden="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
         <v>169</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>170</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>171</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>172</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>173</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>174</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>175</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>176</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>177</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>178</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>179</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>180</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>181</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>182</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>183</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>184</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>185</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>186</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>187</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>188</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>189</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>190</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>191</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>192</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>193</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>194</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>195</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>196</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>197</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>198</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>199</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>200</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>201</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>202</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>203</v>
       </c>
-      <c r="AJ1" t="s">
+    </row>
+    <row r="2" ht="25.05" customHeight="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
         <v>204</v>
       </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-    </row>
-    <row r="3" spans="1:36" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" ht="19.95" customHeight="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="Y3" s="3" t="s">
         <v>230</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>231</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>105</v>
       </c>
       <c r="AA3" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="AB3" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="AJ3" s="3" t="s">
+    </row>
+    <row r="4" ht="16.05" customHeight="1" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
         <v>241</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
-        <v>242</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>144</v>
@@ -2472,10 +2465,10 @@
         <v>131</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>157</v>
@@ -2551,14 +2544,14 @@
     <mergeCell ref="Z2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="3" width="20" customWidth="1"/>
@@ -2566,62 +2559,62 @@
     <col min="5" max="5" width="17.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>244</v>
+      </c>
+      <c r="C1" t="s">
         <v>245</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>246</v>
       </c>
-      <c r="D1" t="s">
+    </row>
+    <row r="2" ht="25.05" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>247</v>
       </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E2" s="2"/>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="19.95" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" ht="16.05" customHeight="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>254</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>255</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>256</v>
       </c>
     </row>
   </sheetData>
@@ -2630,14 +2623,14 @@
     <mergeCell ref="D2:E2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AJ4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="5" width="28" customWidth="1"/>
@@ -2659,275 +2652,275 @@
     <col min="36" max="36" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" hidden="1" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" t="s">
         <v>257</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>258</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>259</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>260</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>261</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>262</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>263</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>264</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>265</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>266</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>267</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>268</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>269</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>270</v>
       </c>
-      <c r="P1" t="s">
+      <c r="Q1" t="s">
         <v>271</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="R1" t="s">
         <v>272</v>
       </c>
-      <c r="R1" t="s">
+      <c r="S1" t="s">
         <v>273</v>
       </c>
-      <c r="S1" t="s">
+      <c r="T1" t="s">
         <v>274</v>
       </c>
-      <c r="T1" t="s">
+      <c r="U1" t="s">
         <v>275</v>
       </c>
-      <c r="U1" t="s">
+      <c r="V1" t="s">
         <v>276</v>
       </c>
-      <c r="V1" t="s">
+      <c r="W1" t="s">
         <v>277</v>
       </c>
-      <c r="W1" t="s">
+      <c r="X1" t="s">
         <v>278</v>
       </c>
-      <c r="X1" t="s">
+      <c r="Y1" t="s">
         <v>279</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>280</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>281</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AB1" t="s">
         <v>282</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>283</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>284</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>285</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>286</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>287</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>288</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>289</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>290</v>
       </c>
-      <c r="AJ1" t="s">
+    </row>
+    <row r="2" ht="25.05" customHeight="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>291</v>
       </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
     </row>
-    <row r="2" spans="1:36" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6" t="s">
-        <v>293</v>
-      </c>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-      <c r="R2" s="6"/>
-      <c r="S2" s="6"/>
-      <c r="T2" s="6"/>
-      <c r="U2" s="6"/>
-      <c r="V2" s="6"/>
-      <c r="W2" s="6"/>
-      <c r="X2" s="6"/>
-      <c r="Y2" s="6"/>
-      <c r="Z2" s="6" t="s">
-        <v>294</v>
-      </c>
-      <c r="AA2" s="6"/>
-      <c r="AB2" s="6"/>
-      <c r="AC2" s="6"/>
-      <c r="AD2" s="6"/>
-      <c r="AE2" s="6"/>
-      <c r="AF2" s="6"/>
-      <c r="AG2" s="6"/>
-      <c r="AH2" s="6"/>
-      <c r="AI2" s="6"/>
-      <c r="AJ2" s="6"/>
-    </row>
-    <row r="3" spans="1:36" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="19.95" customHeight="1" spans="1:36" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="G3" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="I3" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="O3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="P3" s="3" t="s">
+      <c r="Q3" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="R3" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="R3" s="3" t="s">
+      <c r="S3" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="S3" s="3" t="s">
+      <c r="T3" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="T3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="U3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="V3" s="3" t="s">
+      <c r="W3" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="W3" s="3" t="s">
+      <c r="X3" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="X3" s="3" t="s">
+      <c r="Y3" s="3" t="s">
         <v>317</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>318</v>
       </c>
       <c r="Z3" s="3" t="s">
         <v>105</v>
       </c>
       <c r="AA3" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="AB3" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="AB3" s="3" t="s">
+      <c r="AC3" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="AC3" s="3" t="s">
+      <c r="AD3" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AE3" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="AE3" s="3" t="s">
+      <c r="AF3" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="AF3" s="3" t="s">
+      <c r="AG3" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="AG3" s="3" t="s">
+      <c r="AH3" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="AH3" s="3" t="s">
+      <c r="AI3" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="AI3" s="3" t="s">
+      <c r="AJ3" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="AJ3" s="3" t="s">
-        <v>328</v>
-      </c>
     </row>
-    <row r="4" spans="1:36" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" ht="16.05" customHeight="1" spans="1:36" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>144</v>
@@ -2963,10 +2956,10 @@
         <v>131</v>
       </c>
       <c r="M4" s="5" t="s">
+        <v>242</v>
+      </c>
+      <c r="N4" s="5" t="s">
         <v>243</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>244</v>
       </c>
       <c r="O4" s="5" t="s">
         <v>157</v>
@@ -3042,14 +3035,14 @@
     <mergeCell ref="Z2:AJ2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E4"/>
-  <sheetFormatPr defaultRowHeight="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="2" width="45" customWidth="1"/>
     <col min="3" max="3" width="34" customWidth="1"/>
@@ -3057,78 +3050,84 @@
     <col min="5" max="5" width="19.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="1" hidden="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>169</v>
+        <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>328</v>
+      </c>
+      <c r="C1" t="s">
         <v>329</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>330</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>331</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" ht="25.05" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>332</v>
       </c>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
     </row>
-    <row r="2" spans="1:5" s="1" customFormat="1" ht="25.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-    </row>
-    <row r="3" spans="1:5" s="1" customFormat="1" ht="19.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" ht="19.95" customHeight="1" spans="1:5" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" ht="16.05" customHeight="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" s="4" customFormat="1" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="C4" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>339</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>340</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:E2"/>
   </mergeCells>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="B5:B1000" xr:uid="{00000000-0002-0000-0400-000000000000}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B1000">
       <formula1>"Vehicle,Mobile Phone,Cash,Jewellery,Electronics,Documents,Drugs,Arms,Others"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D5:D1000" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B5:B1000">
+      <formula1>"Vehicle,Mobile Phone,Cash,Jewellery,Electronics,Documents,Drugs,Arms,Others"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D1000">
+      <formula1>"Stolen,Recovered,Involved,Seized"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D5:D1000">
       <formula1>"Stolen,Recovered,Involved,Seized"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>